--- a/main/ig/StructureDefinition-fr-lm-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="235">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -429,6 +429,116 @@
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.header.status.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.header.status.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.header.status.coding</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.header.status.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.header.status.directSubject[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-patient
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-devicehttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-health-professionalhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-organisationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-procedure</t>
+  </si>
+  <si>
+    <t>Sujet direct de l'observation si différent du patient, par exemple dans le cas d’une observation portant sur un dispositif implanté. D’autres types de sujets peuvent être autorisés selon les implémentations.</t>
   </si>
   <si>
     <t>fr-lm-observation.header.source</t>
@@ -451,16 +561,6 @@
     <t>fr-lm-entry.header.language</t>
   </si>
   <si>
-    <t>fr-lm-observation.directSubject[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-patient
-https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-devicehttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-health-professionalhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-organisationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-procedure</t>
-  </si>
-  <si>
-    <t>Sujet direct de l'observation si différent du patient, par exemple dans le cas d’une observation portant sur un dispositif implanté. D’autres types de sujets peuvent être autorisés selon les implémentations.</t>
-  </si>
-  <si>
     <t>fr-lm-observation.observationDate[x]</t>
   </si>
   <si>
@@ -481,10 +581,6 @@
   </si>
   <si>
     <t>fr-lm-observation.originalName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Nom de l'observation</t>
@@ -953,13 +1049,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ42"/>
+  <dimension ref="A1:AJ46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="50.82421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="50.82421875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -970,7 +1066,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="196.6875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -984,7 +1080,7 @@
     <col min="26" max="26" width="80.01171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -2731,13 +2827,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2788,7 +2884,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2805,21 +2901,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>73</v>
@@ -2831,15 +2927,17 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>73</v>
@@ -2876,39 +2974,39 @@
         <v>73</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2919,7 +3017,7 @@
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2928,19 +3026,23 @@
         <v>73</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>73</v>
       </c>
@@ -2988,27 +3090,27 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3016,7 +3118,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -3028,19 +3130,23 @@
         <v>73</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>73</v>
       </c>
@@ -3088,10 +3194,10 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -3100,15 +3206,15 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3116,7 +3222,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -3131,13 +3237,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3167,7 +3273,7 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>73</v>
@@ -3188,10 +3294,10 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>79</v>
@@ -3205,10 +3311,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3231,13 +3337,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3288,7 +3394,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3305,10 +3411,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3334,10 +3440,10 @@
         <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3388,7 +3494,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3405,10 +3511,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3416,7 +3522,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -3431,13 +3537,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3488,10 +3594,10 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>79</v>
@@ -3505,10 +3611,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3516,7 +3622,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -3531,13 +3637,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3567,7 +3673,7 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>73</v>
@@ -3588,10 +3694,10 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>79</v>
@@ -3605,10 +3711,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3631,13 +3737,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3688,7 +3794,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3705,10 +3811,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3716,7 +3822,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>79</v>
@@ -3731,13 +3837,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3788,10 +3894,10 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>79</v>
@@ -3805,10 +3911,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3831,13 +3937,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3888,7 +3994,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3905,10 +4011,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3919,7 +4025,7 @@
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -3931,13 +4037,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3988,13 +4094,13 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>73</v>
@@ -4005,10 +4111,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4031,13 +4137,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4067,7 +4173,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4088,7 +4194,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4105,10 +4211,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4116,7 +4222,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>79</v>
@@ -4131,13 +4237,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4167,7 +4273,7 @@
         <v>73</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>73</v>
@@ -4188,10 +4294,10 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>79</v>
@@ -4205,10 +4311,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4231,13 +4337,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4267,7 +4373,7 @@
         <v>73</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>179</v>
+        <v>73</v>
       </c>
       <c r="Z33" t="s" s="2">
         <v>73</v>
@@ -4288,7 +4394,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4305,10 +4411,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4319,7 +4425,7 @@
         <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
@@ -4331,13 +4437,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4367,7 +4473,7 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>182</v>
+        <v>73</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>73</v>
@@ -4388,13 +4494,13 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>73</v>
@@ -4405,10 +4511,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4419,7 +4525,7 @@
         <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>73</v>
@@ -4431,13 +4537,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4467,7 +4573,7 @@
         <v>73</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -4488,13 +4594,13 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>73</v>
@@ -4505,10 +4611,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4531,13 +4637,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4567,7 +4673,7 @@
         <v>73</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>73</v>
@@ -4588,7 +4694,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4605,10 +4711,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4631,13 +4737,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4667,7 +4773,7 @@
         <v>73</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="Z37" t="s" s="2">
         <v>73</v>
@@ -4688,7 +4794,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -4705,10 +4811,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4719,7 +4825,7 @@
         <v>74</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>73</v>
@@ -4734,10 +4840,10 @@
         <v>131</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4767,10 +4873,10 @@
         <v>73</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>194</v>
+        <v>73</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>73</v>
@@ -4788,13 +4894,13 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>73</v>
@@ -4805,10 +4911,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4819,7 +4925,7 @@
         <v>74</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>73</v>
@@ -4831,13 +4937,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4867,7 +4973,7 @@
         <v>73</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>73</v>
+        <v>215</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>73</v>
@@ -4888,13 +4994,13 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>73</v>
@@ -4905,10 +5011,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4919,7 +5025,7 @@
         <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>73</v>
@@ -4931,13 +5037,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4967,7 +5073,7 @@
         <v>73</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>73</v>
+        <v>204</v>
       </c>
       <c r="Z40" t="s" s="2">
         <v>73</v>
@@ -4988,13 +5094,13 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>73</v>
@@ -5005,10 +5111,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5019,7 +5125,7 @@
         <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>73</v>
@@ -5031,13 +5137,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5088,13 +5194,13 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>73</v>
@@ -5105,10 +5211,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5131,13 +5237,13 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>203</v>
+        <v>131</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5167,10 +5273,10 @@
         <v>73</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>73</v>
+        <v>223</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>73</v>
+        <v>224</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>73</v>
@@ -5188,7 +5294,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5200,6 +5306,406 @@
         <v>73</v>
       </c>
       <c r="AJ42" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="237">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -577,6 +577,9 @@
     <t>Type d'observation</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
     <t>LOINC (2.16.840.1.113883.6.1) ou autre</t>
   </si>
   <si>
@@ -654,6 +657,9 @@
     <t>Limite inférieure de l'intervalle</t>
   </si>
   <si>
+    <t>preferred</t>
+  </si>
+  <si>
     <t>(preferred): UCUM for units</t>
   </si>
   <si>
@@ -712,7 +718,7 @@
     <t>Interprétation</t>
   </si>
   <si>
-    <t>(preferred): HL7 Observation Interpretation Codes</t>
+    <t>HL7 Observation Interpretation Codes</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260619134042</t>
@@ -3670,10 +3676,10 @@
         <v>73</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>73</v>
@@ -3711,10 +3717,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3740,10 +3746,10 @@
         <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3794,7 +3800,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3811,10 +3817,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3840,10 +3846,10 @@
         <v>131</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3894,7 +3900,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3911,10 +3917,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3937,13 +3943,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3994,7 +4000,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4011,10 +4017,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4037,13 +4043,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4094,7 +4100,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4111,10 +4117,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4137,13 +4143,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4194,7 +4200,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4211,10 +4217,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4240,10 +4246,10 @@
         <v>80</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4294,7 +4300,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -4311,10 +4317,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4337,13 +4343,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4394,7 +4400,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4411,10 +4417,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4440,10 +4446,10 @@
         <v>80</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4494,7 +4500,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4511,10 +4517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4537,13 +4543,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4570,10 +4576,10 @@
         <v>73</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>73</v>
+        <v>205</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -4594,7 +4600,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4611,10 +4617,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4637,13 +4643,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4670,10 +4676,10 @@
         <v>73</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>73</v>
+        <v>205</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>73</v>
@@ -4694,7 +4700,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4711,10 +4717,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4740,10 +4746,10 @@
         <v>131</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4770,31 +4776,31 @@
         <v>73</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>73</v>
+        <v>205</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -4811,10 +4817,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4840,10 +4846,10 @@
         <v>131</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4870,31 +4876,31 @@
         <v>73</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>73</v>
+        <v>205</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -4911,10 +4917,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4940,10 +4946,10 @@
         <v>131</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4970,31 +4976,31 @@
         <v>73</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>73</v>
+        <v>205</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5011,10 +5017,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5037,13 +5043,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5070,10 +5076,10 @@
         <v>73</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>73</v>
+        <v>205</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Z40" t="s" s="2">
         <v>73</v>
@@ -5094,7 +5100,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -5111,10 +5117,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5140,10 +5146,10 @@
         <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5194,7 +5200,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5211,10 +5217,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5240,10 +5246,10 @@
         <v>131</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5270,31 +5276,31 @@
         <v>73</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5311,10 +5317,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5340,10 +5346,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5394,7 +5400,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -5411,10 +5417,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5440,10 +5446,10 @@
         <v>80</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5494,7 +5500,7 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
@@ -5511,10 +5517,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5537,13 +5543,13 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5594,7 +5600,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -5611,10 +5617,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5637,13 +5643,13 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5694,7 +5700,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
